--- a/docs/topsheet-data-template-v9.xlsx
+++ b/docs/topsheet-data-template-v9.xlsx
@@ -1,38 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. Deal Identity" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Capital Structure" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. Reserve Accounts" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. Counterparties" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Hedging" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. Jurisdictions" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7. Corporate Entities" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8. Covenant Thresholds" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9. KPI Targets" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10. Financial Template" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11. Development Phases" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12. Consent Mechanics" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13. Holdings" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13B. Investors" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13C. Intercreditor" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13D. Enforcement Classes" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14. Period Definition" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15. Management Case" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16. Credit Case" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17. Combined Downside" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18. Actuals" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19. Key Risks" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20. Onboarding Snapshot" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21. Obligations" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22. Distribution Conditions" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="1. Deal Identity" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="2. Capital Structure" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="3. Reserve Accounts" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="4. Counterparties" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="5. Hedging" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="6. Jurisdictions" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="7. Corporate Entities" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="8. Covenant Thresholds" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="9. KPI Scenario Series" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="10. Financial Template" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="11. Development Phases" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="12. Consent Mechanics" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Validation" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="13. Holdings" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="13B. Investors" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="13C. Intercreditor" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="13D. Enforcement Classes" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="14. Period Definition" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="15. Management Case" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="16. Credit Case" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="17. Combined Downside" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="18. Actuals" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="19. Key Risks" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="20. Onboarding Snapshot" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="21. Obligations" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="22. Distribution Conditions" sheetId="26" state="visible" r:id="rId26"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3089,13 +3089,13 @@
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>9. KPI Targets</t>
+          <t>9. KPI Scenario Series</t>
         </is>
       </c>
       <c r="B11" s="13" t="n"/>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>3-5 sector KPIs recommended</t>
+          <t>Management case + stresses (time series per KPI)</t>
         </is>
       </c>
     </row>
@@ -49570,65 +49570,59 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>IC MEMO KPI TARGETS — Frozen at ingestion. Base case and stress case.</t>
+    <row r="1" ht="55" customHeight="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>IC MEMO KPI SCENARIO SERIES — One row per (scenario × period × KPI) trajectory point. Management case = IC baseline. Single-variant stresses link to a risk_id from Tab 6 risk register. Combined downside is the aggregate stress scenario. Sparse: only fill the rows the IC defined.</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>KPI Name</t>
+          <t>kpi_key</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Base Case Value</t>
+          <t>kpi_label</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Stress Case Value</t>
+          <t>scenario_kind</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>Target Floor</t>
+          <t>stress_label</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>Target Ceiling</t>
+          <t>driving_risk_ref</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>period_flag</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>Unit</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>Source</t>
+          <t>value</t>
         </is>
       </c>
     </row>
@@ -49640,7 +49634,6 @@
       <c r="E3" s="7" t="n"/>
       <c r="F3" s="7" t="n"/>
       <c r="G3" s="7" t="n"/>
-      <c r="H3" s="7" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n"/>
@@ -49650,7 +49643,6 @@
       <c r="E4" s="7" t="n"/>
       <c r="F4" s="7" t="n"/>
       <c r="G4" s="7" t="n"/>
-      <c r="H4" s="7" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n"/>
@@ -49660,7 +49652,6 @@
       <c r="E5" s="7" t="n"/>
       <c r="F5" s="7" t="n"/>
       <c r="G5" s="7" t="n"/>
-      <c r="H5" s="7" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n"/>
@@ -49670,7 +49661,6 @@
       <c r="E6" s="7" t="n"/>
       <c r="F6" s="7" t="n"/>
       <c r="G6" s="7" t="n"/>
-      <c r="H6" s="7" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n"/>
@@ -49680,7 +49670,6 @@
       <c r="E7" s="7" t="n"/>
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="7" t="n"/>
-      <c r="H7" s="7" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n"/>
@@ -49690,7 +49679,6 @@
       <c r="E8" s="7" t="n"/>
       <c r="F8" s="7" t="n"/>
       <c r="G8" s="7" t="n"/>
-      <c r="H8" s="7" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n"/>
@@ -49700,7 +49688,6 @@
       <c r="E9" s="7" t="n"/>
       <c r="F9" s="7" t="n"/>
       <c r="G9" s="7" t="n"/>
-      <c r="H9" s="7" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n"/>
@@ -49710,7 +49697,6 @@
       <c r="E10" s="7" t="n"/>
       <c r="F10" s="7" t="n"/>
       <c r="G10" s="7" t="n"/>
-      <c r="H10" s="7" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n"/>
@@ -49720,7 +49706,6 @@
       <c r="E11" s="7" t="n"/>
       <c r="F11" s="7" t="n"/>
       <c r="G11" s="7" t="n"/>
-      <c r="H11" s="7" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n"/>
@@ -49730,7 +49715,6 @@
       <c r="E12" s="7" t="n"/>
       <c r="F12" s="7" t="n"/>
       <c r="G12" s="7" t="n"/>
-      <c r="H12" s="7" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n"/>
@@ -49740,7 +49724,6 @@
       <c r="E13" s="7" t="n"/>
       <c r="F13" s="7" t="n"/>
       <c r="G13" s="7" t="n"/>
-      <c r="H13" s="7" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n"/>
@@ -49750,21 +49733,449 @@
       <c r="E14" s="7" t="n"/>
       <c r="F14" s="7" t="n"/>
       <c r="G14" s="7" t="n"/>
-      <c r="H14" s="7" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="n"/>
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="7" t="n"/>
+      <c r="E15" s="7" t="n"/>
+      <c r="F15" s="7" t="n"/>
+      <c r="G15" s="7" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="n"/>
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="7" t="n"/>
+      <c r="E16" s="7" t="n"/>
+      <c r="F16" s="7" t="n"/>
+      <c r="G16" s="7" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="n"/>
+      <c r="B17" s="7" t="n"/>
+      <c r="C17" s="7" t="n"/>
+      <c r="D17" s="7" t="n"/>
+      <c r="E17" s="7" t="n"/>
+      <c r="F17" s="7" t="n"/>
+      <c r="G17" s="7" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="n"/>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="n"/>
+      <c r="D18" s="7" t="n"/>
+      <c r="E18" s="7" t="n"/>
+      <c r="F18" s="7" t="n"/>
+      <c r="G18" s="7" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="n"/>
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="7" t="n"/>
+      <c r="D19" s="7" t="n"/>
+      <c r="E19" s="7" t="n"/>
+      <c r="F19" s="7" t="n"/>
+      <c r="G19" s="7" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="n"/>
+      <c r="B20" s="7" t="n"/>
+      <c r="C20" s="7" t="n"/>
+      <c r="D20" s="7" t="n"/>
+      <c r="E20" s="7" t="n"/>
+      <c r="F20" s="7" t="n"/>
+      <c r="G20" s="7" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="n"/>
+      <c r="B21" s="7" t="n"/>
+      <c r="C21" s="7" t="n"/>
+      <c r="D21" s="7" t="n"/>
+      <c r="E21" s="7" t="n"/>
+      <c r="F21" s="7" t="n"/>
+      <c r="G21" s="7" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="n"/>
+      <c r="B22" s="7" t="n"/>
+      <c r="C22" s="7" t="n"/>
+      <c r="D22" s="7" t="n"/>
+      <c r="E22" s="7" t="n"/>
+      <c r="F22" s="7" t="n"/>
+      <c r="G22" s="7" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="n"/>
+      <c r="B23" s="7" t="n"/>
+      <c r="C23" s="7" t="n"/>
+      <c r="D23" s="7" t="n"/>
+      <c r="E23" s="7" t="n"/>
+      <c r="F23" s="7" t="n"/>
+      <c r="G23" s="7" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="n"/>
+      <c r="B24" s="7" t="n"/>
+      <c r="C24" s="7" t="n"/>
+      <c r="D24" s="7" t="n"/>
+      <c r="E24" s="7" t="n"/>
+      <c r="F24" s="7" t="n"/>
+      <c r="G24" s="7" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="n"/>
+      <c r="B25" s="7" t="n"/>
+      <c r="C25" s="7" t="n"/>
+      <c r="D25" s="7" t="n"/>
+      <c r="E25" s="7" t="n"/>
+      <c r="F25" s="7" t="n"/>
+      <c r="G25" s="7" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="n"/>
+      <c r="B26" s="7" t="n"/>
+      <c r="C26" s="7" t="n"/>
+      <c r="D26" s="7" t="n"/>
+      <c r="E26" s="7" t="n"/>
+      <c r="F26" s="7" t="n"/>
+      <c r="G26" s="7" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="n"/>
+      <c r="B27" s="7" t="n"/>
+      <c r="C27" s="7" t="n"/>
+      <c r="D27" s="7" t="n"/>
+      <c r="E27" s="7" t="n"/>
+      <c r="F27" s="7" t="n"/>
+      <c r="G27" s="7" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n"/>
+      <c r="B28" s="7" t="n"/>
+      <c r="C28" s="7" t="n"/>
+      <c r="D28" s="7" t="n"/>
+      <c r="E28" s="7" t="n"/>
+      <c r="F28" s="7" t="n"/>
+      <c r="G28" s="7" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="n"/>
+      <c r="B29" s="7" t="n"/>
+      <c r="C29" s="7" t="n"/>
+      <c r="D29" s="7" t="n"/>
+      <c r="E29" s="7" t="n"/>
+      <c r="F29" s="7" t="n"/>
+      <c r="G29" s="7" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="n"/>
+      <c r="B30" s="7" t="n"/>
+      <c r="C30" s="7" t="n"/>
+      <c r="D30" s="7" t="n"/>
+      <c r="E30" s="7" t="n"/>
+      <c r="F30" s="7" t="n"/>
+      <c r="G30" s="7" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="n"/>
+      <c r="B31" s="7" t="n"/>
+      <c r="C31" s="7" t="n"/>
+      <c r="D31" s="7" t="n"/>
+      <c r="E31" s="7" t="n"/>
+      <c r="F31" s="7" t="n"/>
+      <c r="G31" s="7" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="n"/>
+      <c r="B32" s="7" t="n"/>
+      <c r="C32" s="7" t="n"/>
+      <c r="D32" s="7" t="n"/>
+      <c r="E32" s="7" t="n"/>
+      <c r="F32" s="7" t="n"/>
+      <c r="G32" s="7" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="n"/>
+      <c r="B33" s="7" t="n"/>
+      <c r="C33" s="7" t="n"/>
+      <c r="D33" s="7" t="n"/>
+      <c r="E33" s="7" t="n"/>
+      <c r="F33" s="7" t="n"/>
+      <c r="G33" s="7" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="n"/>
+      <c r="B34" s="7" t="n"/>
+      <c r="C34" s="7" t="n"/>
+      <c r="D34" s="7" t="n"/>
+      <c r="E34" s="7" t="n"/>
+      <c r="F34" s="7" t="n"/>
+      <c r="G34" s="7" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="n"/>
+      <c r="B35" s="7" t="n"/>
+      <c r="C35" s="7" t="n"/>
+      <c r="D35" s="7" t="n"/>
+      <c r="E35" s="7" t="n"/>
+      <c r="F35" s="7" t="n"/>
+      <c r="G35" s="7" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="n"/>
+      <c r="B36" s="7" t="n"/>
+      <c r="C36" s="7" t="n"/>
+      <c r="D36" s="7" t="n"/>
+      <c r="E36" s="7" t="n"/>
+      <c r="F36" s="7" t="n"/>
+      <c r="G36" s="7" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="n"/>
+      <c r="B37" s="7" t="n"/>
+      <c r="C37" s="7" t="n"/>
+      <c r="D37" s="7" t="n"/>
+      <c r="E37" s="7" t="n"/>
+      <c r="F37" s="7" t="n"/>
+      <c r="G37" s="7" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="n"/>
+      <c r="B38" s="7" t="n"/>
+      <c r="C38" s="7" t="n"/>
+      <c r="D38" s="7" t="n"/>
+      <c r="E38" s="7" t="n"/>
+      <c r="F38" s="7" t="n"/>
+      <c r="G38" s="7" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="n"/>
+      <c r="B39" s="7" t="n"/>
+      <c r="C39" s="7" t="n"/>
+      <c r="D39" s="7" t="n"/>
+      <c r="E39" s="7" t="n"/>
+      <c r="F39" s="7" t="n"/>
+      <c r="G39" s="7" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="n"/>
+      <c r="B40" s="7" t="n"/>
+      <c r="C40" s="7" t="n"/>
+      <c r="D40" s="7" t="n"/>
+      <c r="E40" s="7" t="n"/>
+      <c r="F40" s="7" t="n"/>
+      <c r="G40" s="7" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="n"/>
+      <c r="B41" s="7" t="n"/>
+      <c r="C41" s="7" t="n"/>
+      <c r="D41" s="7" t="n"/>
+      <c r="E41" s="7" t="n"/>
+      <c r="F41" s="7" t="n"/>
+      <c r="G41" s="7" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="n"/>
+      <c r="B42" s="7" t="n"/>
+      <c r="C42" s="7" t="n"/>
+      <c r="D42" s="7" t="n"/>
+      <c r="E42" s="7" t="n"/>
+      <c r="F42" s="7" t="n"/>
+      <c r="G42" s="7" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="n"/>
+      <c r="B43" s="7" t="n"/>
+      <c r="C43" s="7" t="n"/>
+      <c r="D43" s="7" t="n"/>
+      <c r="E43" s="7" t="n"/>
+      <c r="F43" s="7" t="n"/>
+      <c r="G43" s="7" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="n"/>
+      <c r="B44" s="7" t="n"/>
+      <c r="C44" s="7" t="n"/>
+      <c r="D44" s="7" t="n"/>
+      <c r="E44" s="7" t="n"/>
+      <c r="F44" s="7" t="n"/>
+      <c r="G44" s="7" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="n"/>
+      <c r="B45" s="7" t="n"/>
+      <c r="C45" s="7" t="n"/>
+      <c r="D45" s="7" t="n"/>
+      <c r="E45" s="7" t="n"/>
+      <c r="F45" s="7" t="n"/>
+      <c r="G45" s="7" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="n"/>
+      <c r="B46" s="7" t="n"/>
+      <c r="C46" s="7" t="n"/>
+      <c r="D46" s="7" t="n"/>
+      <c r="E46" s="7" t="n"/>
+      <c r="F46" s="7" t="n"/>
+      <c r="G46" s="7" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="n"/>
+      <c r="B47" s="7" t="n"/>
+      <c r="C47" s="7" t="n"/>
+      <c r="D47" s="7" t="n"/>
+      <c r="E47" s="7" t="n"/>
+      <c r="F47" s="7" t="n"/>
+      <c r="G47" s="7" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="n"/>
+      <c r="B48" s="7" t="n"/>
+      <c r="C48" s="7" t="n"/>
+      <c r="D48" s="7" t="n"/>
+      <c r="E48" s="7" t="n"/>
+      <c r="F48" s="7" t="n"/>
+      <c r="G48" s="7" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="n"/>
+      <c r="B49" s="7" t="n"/>
+      <c r="C49" s="7" t="n"/>
+      <c r="D49" s="7" t="n"/>
+      <c r="E49" s="7" t="n"/>
+      <c r="F49" s="7" t="n"/>
+      <c r="G49" s="7" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="n"/>
+      <c r="B50" s="7" t="n"/>
+      <c r="C50" s="7" t="n"/>
+      <c r="D50" s="7" t="n"/>
+      <c r="E50" s="7" t="n"/>
+      <c r="F50" s="7" t="n"/>
+      <c r="G50" s="7" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="n"/>
+      <c r="B51" s="7" t="n"/>
+      <c r="C51" s="7" t="n"/>
+      <c r="D51" s="7" t="n"/>
+      <c r="E51" s="7" t="n"/>
+      <c r="F51" s="7" t="n"/>
+      <c r="G51" s="7" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="n"/>
+      <c r="B52" s="7" t="n"/>
+      <c r="C52" s="7" t="n"/>
+      <c r="D52" s="7" t="n"/>
+      <c r="E52" s="7" t="n"/>
+      <c r="F52" s="7" t="n"/>
+      <c r="G52" s="7" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="n"/>
+      <c r="B53" s="7" t="n"/>
+      <c r="C53" s="7" t="n"/>
+      <c r="D53" s="7" t="n"/>
+      <c r="E53" s="7" t="n"/>
+      <c r="F53" s="7" t="n"/>
+      <c r="G53" s="7" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="n"/>
+      <c r="B54" s="7" t="n"/>
+      <c r="C54" s="7" t="n"/>
+      <c r="D54" s="7" t="n"/>
+      <c r="E54" s="7" t="n"/>
+      <c r="F54" s="7" t="n"/>
+      <c r="G54" s="7" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="n"/>
+      <c r="B55" s="7" t="n"/>
+      <c r="C55" s="7" t="n"/>
+      <c r="D55" s="7" t="n"/>
+      <c r="E55" s="7" t="n"/>
+      <c r="F55" s="7" t="n"/>
+      <c r="G55" s="7" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="n"/>
+      <c r="B56" s="7" t="n"/>
+      <c r="C56" s="7" t="n"/>
+      <c r="D56" s="7" t="n"/>
+      <c r="E56" s="7" t="n"/>
+      <c r="F56" s="7" t="n"/>
+      <c r="G56" s="7" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="n"/>
+      <c r="B57" s="7" t="n"/>
+      <c r="C57" s="7" t="n"/>
+      <c r="D57" s="7" t="n"/>
+      <c r="E57" s="7" t="n"/>
+      <c r="F57" s="7" t="n"/>
+      <c r="G57" s="7" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="n"/>
+      <c r="B58" s="7" t="n"/>
+      <c r="C58" s="7" t="n"/>
+      <c r="D58" s="7" t="n"/>
+      <c r="E58" s="7" t="n"/>
+      <c r="F58" s="7" t="n"/>
+      <c r="G58" s="7" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="n"/>
+      <c r="B59" s="7" t="n"/>
+      <c r="C59" s="7" t="n"/>
+      <c r="D59" s="7" t="n"/>
+      <c r="E59" s="7" t="n"/>
+      <c r="F59" s="7" t="n"/>
+      <c r="G59" s="7" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="n"/>
+      <c r="B60" s="7" t="n"/>
+      <c r="C60" s="7" t="n"/>
+      <c r="D60" s="7" t="n"/>
+      <c r="E60" s="7" t="n"/>
+      <c r="F60" s="7" t="n"/>
+      <c r="G60" s="7" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="n"/>
+      <c r="B61" s="7" t="n"/>
+      <c r="C61" s="7" t="n"/>
+      <c r="D61" s="7" t="n"/>
+      <c r="E61" s="7" t="n"/>
+      <c r="F61" s="7" t="n"/>
+      <c r="G61" s="7" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="n"/>
+      <c r="B62" s="7" t="n"/>
+      <c r="C62" s="7" t="n"/>
+      <c r="D62" s="7" t="n"/>
+      <c r="E62" s="7" t="n"/>
+      <c r="F62" s="7" t="n"/>
+      <c r="G62" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <dataValidations count="3">
-    <dataValidation sqref="F3 F4 F5 F6 F7 F8 F9 F10 F11 F12 F13 F14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"higher_is_better,lower_is_better,range"</formula1>
+  <dataValidations count="2">
+    <dataValidation sqref="A3 A4 A5 A6 A7 A8 A9 A10 A11 A12 A13 A14 A15 A16 A17 A18 A19 A20 A21 A22 A23 A24 A25 A26 A27 A28 A29 A30 A31 A32 A33 A34 A35 A36 A37 A38 A39 A40 A41 A42 A43 A44 A45 A46 A47 A48 A49 A50 A51 A52 A53 A54 A55 A56 A57 A58 A59 A60 A61 A62" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"sector_kpi_1,sector_kpi_2,sector_kpi_3,sector_kpi_4,sector_kpi_5,sector_kpi_6,sector_kpi_7,sector_kpi_8,sector_kpi_9,sector_kpi_10"</formula1>
     </dataValidation>
-    <dataValidation sqref="G3 G4 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"percentage,currency,count,ratio,years,bps"</formula1>
-    </dataValidation>
-    <dataValidation sqref="H3 H4 H5 H6 H7 H8 H9 H10 H11 H12 H13 H14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>"ic_memo,business_plan,management_presentation,lender_model"</formula1>
+    <dataValidation sqref="C3 C4 C5 C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 C21 C22 C23 C24 C25 C26 C27 C28 C29 C30 C31 C32 C33 C34 C35 C36 C37 C38 C39 C40 C41 C42 C43 C44 C45 C46 C47 C48 C49 C50 C51 C52 C53 C54 C55 C56 C57 C58 C59 C60 C61 C62" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"management_case,single_variant_stress,combined_downside,credit_case,lender_case,custom"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
